--- a/VendorInfo.xlsx
+++ b/VendorInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jesus\Desktop\WinFormsApp-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198049FB-4059-4AAB-A5A8-01C9D478068D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2CCC64-3E44-4B33-8339-B3FDE385D02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="690" windowWidth="26655" windowHeight="11295" xr2:uid="{5F3B18D5-44BA-4945-B1D6-A7140318F147}"/>
+    <workbookView xWindow="0" yWindow="1485" windowWidth="26655" windowHeight="11295" xr2:uid="{5F3B18D5-44BA-4945-B1D6-A7140318F147}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -87,6 +87,21 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Bears</t>
+  </si>
+  <si>
+    <t>National Geographoc</t>
+  </si>
+  <si>
+    <t>Baldwin City</t>
+  </si>
+  <si>
+    <t>Green Tea</t>
+  </si>
+  <si>
+    <t>Cream</t>
   </si>
 </sst>
 </file>
@@ -458,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2656B108-B7AC-4657-9073-B850193AF5D5}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -523,6 +538,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
